--- a/Documentacion/1. Story Points y Asignacion de Responsabilidades.xlsx
+++ b/Documentacion/1. Story Points y Asignacion de Responsabilidades.xlsx
@@ -32,6 +32,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={04CB6911-E216-5FFA-A00E-331AF1FB8FD4}</author>
+    <author>tc={6A98EA58-EBE2-D560-1FEC-96EE11A8B0CE}</author>
   </authors>
   <commentList>
     <comment ref="C4" authorId="0" xr:uid="{04CB6911-E216-5FFA-A00E-331AF1FB8FD4}">
@@ -59,12 +60,33 @@
         </r>
       </text>
     </comment>
+    <comment ref="D4" authorId="1" xr:uid="{6A98EA58-EBE2-D560-1FEC-96EE11A8B0CE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>AskingMansOz:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+21.6 x Persona
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t xml:space="preserve">Integrantes Proyecto</t>
   </si>
@@ -81,7 +103,7 @@
     <t xml:space="preserve">Brandon Guido Navarro</t>
   </si>
   <si>
-    <t xml:space="preserve">Sebastián Obando</t>
+    <t xml:space="preserve">Sebastián Obando Ramírez</t>
   </si>
   <si>
     <t xml:space="preserve">Julián Solano Obando</t>
@@ -102,9 +124,6 @@
     <t xml:space="preserve">Historia de Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">Resumen Historia de Usuario (Justificación Story Points)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Story Points</t>
   </si>
   <si>
@@ -120,45 +139,30 @@
     <t xml:space="preserve">Servicio para Administrar Usuarios</t>
   </si>
   <si>
-    <t xml:space="preserve">Sube del CRUD estándar. Son 6 operaciones (una extra con filtros por identificación, nombre y tipo) y reglas de negocio propias: el dominio del email (cuc.cr o cuc.ac.cr) define qué rol es válido, el email es la llave única, la contraseña se guarda encriptada y los tipos de identificación deben poder extenderse. Se debe implementar token y bitácora.</t>
-  </si>
-  <si>
     <t>USR2</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Roles</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar. 5 operaciones sobre una entidad de 2 campos (identificador y nombre) con una sola validación (nombre solo letras y espacios), más token y bitácora.</t>
-  </si>
-  <si>
     <t>USR3</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Parametrización</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar. 5 operaciones sobre 2 campos (identificador y valor) con validaciones de formato (identificador de máximo 10 letras mayúsculas, valor de máximo 500 caracteres), más token y bitácora. Otras HU consumen sus valores, pero ese costo va en cada HU consumidora. Se debe implementar token y bitácora.</t>
-  </si>
-  <si>
     <t>USR4</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Módulos</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar. 5 operaciones sobre 2 campos (identificador y nombre), con validación de nombre solo letras y espacios, más token y bitácora.</t>
-  </si>
-  <si>
     <t>USR5</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Login</t>
   </si>
   <si>
-    <t xml:space="preserve">Login fijado en 5 por su complejidad base. 3 endpoints (/login, /refresh, /validate): /login verifica usuario y contraseña encriptada y responde 201 o 401, genera JWT y refresh token con expiración parametrizable; /refresh y /validate los consumen. Es crítico porque todas las demás HU validan su token contra /validate. Se debe implementar bitácora.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oferta acádecima</t>
   </si>
   <si>
@@ -168,54 +172,36 @@
     <t xml:space="preserve">Servicio para Administrar Instituciones</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar. 5 operaciones sobre 2 campos (identificador y nombre de la institución), con validación de nombre solo letras y espacios, más token y bitácora.</t>
-  </si>
-  <si>
     <t>ACD2</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Carreras</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar de 4 campos (identificador, nombre, institución y director). Suma una consulta por institución y dos validaciones de existencia (la institución y que el director sea un profesor de ACD6), pero son lecturas, no lógica de negocio. Se debe implementar token y bitácora.</t>
-  </si>
-  <si>
     <t>ACD3</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Cursos</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar de 4 campos con una operación extra (cursos por carrera, 6 en total). Valida que la carrera exista y que el nivel esté entre 1 y 12. Se debe implementar token y bitácora.</t>
-  </si>
-  <si>
     <t>ACD4</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Grupos</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar de 7 campos con 3 relaciones (curso, profesor y periodo) más número, horario y cupo. Todo son validaciones de campo y de existencia; los criterios no piden reglas de negocio adicionales. Se debe implementar token y bitácora.</t>
-  </si>
-  <si>
     <t>ACD5</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Periodos</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar de 5 operaciones sobre 4 campos (año, número de periodo, fecha de inicio y fecha de fin); los criterios solo exigen que sean obligatorios, más token y bitácora.</t>
-  </si>
-  <si>
     <t>ACD6</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Profesores</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar de 6 campos. Suma validaciones de formato (nombre solo letras, mayor de edad, email del dominio parametrizable) y teléfonos múltiples, pero son validaciones de campo, no lógica de negocio. Se debe implementar token y bitácora. </t>
-  </si>
-  <si>
     <t>Matrícula</t>
   </si>
   <si>
@@ -225,45 +211,30 @@
     <t xml:space="preserve">Servicio para Administrar Pre-Matrícula</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar con encabezado (estudiante, carrera, periodo y observaciones opcionales) y lista de cursos. Las reglas (solo cursos de primer nivel y periodos futuros) son validaciones de lectura contra ACD3 y ACD5; no hay cálculos ni cambios de estado en otras entidades. Se debe implementar token y bitácora. </t>
-  </si>
-  <si>
     <t>MAT2</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Matrícula</t>
   </si>
   <si>
-    <t xml:space="preserve">Una operación menos que un CRUD (4: matricular, modificar, eliminar y consultar estudiantes por curso y grupo), pero contiene validaciones cruzadas: periodo activo y existencia de estudiante, curso y grupo. No calcula ni cambia estados en otras entidades. Se debe implementar token y bitácora. </t>
-  </si>
-  <si>
     <t>MAT3</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Expedientes de Estudiantes</t>
   </si>
   <si>
-    <t xml:space="preserve">CRUD estándar de 7 campos (identificación, tipo, email, nombre, fecha de nacimiento, dirección estructurada y teléfonos múltiples). Suma validaciones de formato (nombre solo letras, email con dominio parametrizable), sin lógica de negocio. Se debe implementar token y bitácora. </t>
-  </si>
-  <si>
     <t>MAT4</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Direcciones</t>
   </si>
   <si>
-    <t xml:space="preserve">Solo lectura. 3 consultas (/provincias, /cantones y /distritos) que no crean ni modifican datos. La única regla es que el cantón corresponda a la provincia; el trabajo extra es cargar el catálogo geográfico. Se debe implementar token y bitácora. </t>
-  </si>
-  <si>
     <t>MAT5</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Admininstrar Notas</t>
   </si>
   <si>
-    <t xml:space="preserve">Sube del CRUD por reglas de negocio con estado que controlar. 4 operaciones donde los rubros de un desglose deben sumar 100, cargar un desglose nuevo reemplaza el anterior, los rubros no se pueden modificar una vez asignadas notas y cada nota debe ir de 1 a 100. Se debe implementar token y bitácora. </t>
-  </si>
-  <si>
     <t>Académico</t>
   </si>
   <si>
@@ -273,18 +244,12 @@
     <t xml:space="preserve">Servicio para Consultar Historial Académico</t>
   </si>
   <si>
-    <t xml:space="preserve">Un solo endpoint de solo lectura (/historialacademico) que devuelve código, nombre y promedio por curso. No escribe ni cambia estados. Se debe implementar token y bitácora. </t>
-  </si>
-  <si>
     <t>ACA2</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Consultar Listado de Estudiantes</t>
   </si>
   <si>
-    <t xml:space="preserve">Un solo endpoint de solo lectura (/listadoestudiantes) que recibe un periodo y devuelve 7 datos por estudiante. Solo une información de otras entidades (estudiante, carrera, curso y grupo), sin cálculos.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Integración de pagos y notificaciones</t>
   </si>
   <si>
@@ -294,27 +259,18 @@
     <t xml:space="preserve">Servicio para Administrar Facturación</t>
   </si>
   <si>
-    <t xml:space="preserve">Sube del CRUD por lógica de negocio. 4 operaciones con patrón encabezado-detalle obligatorio, monto de 30.000 colones más impuesto del 2 %, detalle fijo "Servicios estudiantiles", estado inicial pendiente y anulación (reverso) de facturas. Se debe implementar token y bitácora.</t>
-  </si>
-  <si>
     <t>IPN2</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Administrar Pagos</t>
   </si>
   <si>
-    <t xml:space="preserve">Sube del CRUD por manejo de estados entre entidades. Crear un pago marca la factura como pagada y reversarlo la devuelve a pendiente, por lo que factura y pago deben mantenerse consistentes. 4 operaciones (crear, reversar, obtener uno y listar por periodo). Se debe implementar token y bitácora.</t>
-  </si>
-  <si>
     <t>IPN3</t>
   </si>
   <si>
     <t xml:space="preserve">Servicio para Gestiónar Notificaciones</t>
   </si>
   <si>
-    <t xml:space="preserve">Un solo endpoint (/notificar), pero con dependencia externa: envía correo con cuerpo HTML por un servidor de correo cuyos datos (servidor y cuenta) son parametrizables. Se debe implementar token y bitácora.</t>
-  </si>
-  <si>
     <t>General</t>
   </si>
   <si>
@@ -322,9 +278,6 @@
   </si>
   <si>
     <t xml:space="preserve">Servicio para Registrar y Consultar Bitácoras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Técnicamente simple (2 endpoint /bitacora con 2 parámetros y fecha automática), pero es transversal: todos los demás servicios deben invocarlo para registrar cada operación de CRUD y cada error técnico. Además está implícito, se debe consultar el historial de bitácora.</t>
   </si>
 </sst>
 </file>
@@ -624,7 +577,7 @@
     <xf fontId="2" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
     <xf fontId="3" fillId="4" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="47">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -666,9 +619,6 @@
     <xf fontId="4" fillId="9" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="9" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="6" fillId="0" borderId="8" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -681,9 +631,6 @@
     <xf fontId="4" fillId="9" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="9" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="6" fillId="0" borderId="10" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -696,9 +643,6 @@
     <xf fontId="4" fillId="9" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="9" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="6" fillId="0" borderId="12" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -711,9 +655,6 @@
     <xf fontId="4" fillId="10" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="10" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="6" fillId="0" borderId="8" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -726,9 +667,6 @@
     <xf fontId="4" fillId="10" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="10" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="4" fillId="10" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -738,9 +676,6 @@
     <xf fontId="4" fillId="10" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="10" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="4" fillId="10" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -767,9 +702,6 @@
     </xf>
     <xf fontId="4" fillId="10" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="6" fillId="0" borderId="14" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -805,7 +737,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="AskingMansOz" id="{CE720F10-A9C9-3E8C-67D9-3B74414113DB}" userId="AskingMansOz" providerId="Teamlab"/>
+  <person displayName="AskingMansOz" id="{A36F4E31-68DB-11C5-CF8D-E4A86219E6FC}" userId="AskingMansOz" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -1289,12 +1221,16 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C4" dT="2026-09-19T09:13:08.03Z" personId="{CE720F10-A9C9-3E8C-67D9-3B74414113DB}" id="{04CB6911-E216-5FFA-A00E-331AF1FB8FD4}" done="0">
+  <threadedComment ref="C4" dT="2026-09-19T09:13:08.03Z" personId="{A36F4E31-68DB-11C5-CF8D-E4A86219E6FC}" id="{04CB6911-E216-5FFA-A00E-331AF1FB8FD4}" done="0">
     <text xml:space="preserve">Mide la carga de trabajo del equipo con base en el promedio de puntos acumulados por los integrantes:
 * Verde: Por debajo del promedio (menor carga).
 * Amarillo: En el promedio exacto (carga equilibrada).
 * Rojo: Por encima del promedio (sobrecarga de trabajo).
 Lo ideal es que la carga de trabajo se mantengan cerca del promedio.
+</text>
+  </threadedComment>
+  <threadedComment ref="D4" dT="2026-09-25T19:25:05.93Z" personId="{A36F4E31-68DB-11C5-CF8D-E4A86219E6FC}" id="{6A98EA58-EBE2-D560-1FEC-96EE11A8B0CE}" done="0">
+    <text xml:space="preserve">21.6 x Persona
 </text>
   </threadedComment>
 </ThreadedComments>
@@ -1304,11 +1240,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" min="2" max="2" width="33"/>
+    <col customWidth="1" min="2" max="2" width="33.28125"/>
     <col customWidth="1" min="3" max="3" width="17.140625"/>
     <col customWidth="1" min="4" max="4" width="47.7109375"/>
-    <col customWidth="1" min="5" max="5" style="1" width="70.140625"/>
-    <col customWidth="1" min="6" max="6" width="12.140625"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" style="1" width="11.34375"/>
+    <col customWidth="1" min="6" max="6" width="27.00390625"/>
     <col customWidth="1" min="7" max="7" width="18.421875"/>
     <col bestFit="1" customWidth="1" min="8" max="8" width="11.421875"/>
     <col bestFit="1" min="9" max="9" width="11.421875"/>
@@ -1337,12 +1273,12 @@
         <v>3</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C8" si="0">SUMIF($G$13:$G$100,B4,$F$13:$F$100)</f>
-        <v>0</v>
+        <f t="shared" ref="C4:C8" si="0">SUMIF($F$13:$F$100,B4,$E$13:$E$100)</f>
+        <v>21</v>
       </c>
       <c r="D4" s="6">
-        <f t="shared" ref="D4:D8" si="1">COUNTIF($G$13:$G$100,B4)</f>
-        <v>0</v>
+        <f t="shared" ref="D4:D8" si="1">COUNTIF($E$13:$F$100,B4)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1351,11 +1287,11 @@
       </c>
       <c r="C5" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="42.75">
@@ -1364,11 +1300,11 @@
       </c>
       <c r="C6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="28.5">
@@ -1377,11 +1313,11 @@
       </c>
       <c r="C7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -1390,11 +1326,11 @@
       </c>
       <c r="C8" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D8" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" s="10"/>
     </row>
@@ -1404,7 +1340,7 @@
       </c>
       <c r="C9" s="12">
         <f>SUM(C4:C8)</f>
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" ht="15"/>
@@ -1425,416 +1361,392 @@
       <c r="F12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="13" ht="71.25">
       <c r="B13" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="E13" s="15">
+        <v>8</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" ht="42.75">
+      <c r="B14" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="D14" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="16">
+      <c r="E14" s="19">
+        <v>5</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" ht="71.25">
+      <c r="B15" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="19">
+        <v>5</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" ht="28.5">
+      <c r="B16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="19">
+        <v>5</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" ht="71.25">
+      <c r="B17" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="23">
         <v>8</v>
       </c>
-      <c r="G13" s="17"/>
-    </row>
-    <row r="14" ht="42.75">
-      <c r="B14" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="21">
-        <v>5</v>
-      </c>
-      <c r="G14" s="22"/>
-    </row>
-    <row r="15" ht="71.25">
-      <c r="B15" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="21">
-        <v>5</v>
-      </c>
-      <c r="G15" s="22"/>
-    </row>
-    <row r="16" ht="28.5">
-      <c r="B16" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="F17" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" ht="42.75">
+      <c r="B18" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="C18" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="D18" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="21">
-        <v>5</v>
-      </c>
-      <c r="G16" s="22"/>
-    </row>
-    <row r="17" ht="71.25">
-      <c r="B17" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="24" t="s">
+      <c r="E18" s="27">
+        <v>5</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" ht="57">
+      <c r="B19" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D19" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E19" s="19">
+        <v>5</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" ht="42.75">
+      <c r="B20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="26">
-        <v>5</v>
-      </c>
-      <c r="G17" s="27"/>
-    </row>
-    <row r="18" ht="42.75">
-      <c r="B18" s="28" t="s">
+      <c r="D20" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="E20" s="19">
+        <v>5</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" ht="57">
+      <c r="B21" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D21" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E21" s="19">
+        <v>5</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" ht="42.75">
+      <c r="B22" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="31">
-        <v>5</v>
-      </c>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" ht="57">
-      <c r="B19" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="34" t="s">
+      <c r="D22" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E22" s="19">
+        <v>5</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" ht="57">
+      <c r="B23" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="D23" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="21">
-        <v>5</v>
-      </c>
-      <c r="G19" s="36"/>
-    </row>
-    <row r="20" ht="42.75">
-      <c r="B20" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="21">
-        <v>5</v>
-      </c>
-      <c r="G20" s="36"/>
-    </row>
-    <row r="21" ht="57">
-      <c r="B21" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="21">
-        <v>5</v>
-      </c>
-      <c r="G21" s="36"/>
-    </row>
-    <row r="22" ht="42.75">
-      <c r="B22" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="21">
-        <v>5</v>
-      </c>
-      <c r="G22" s="36"/>
-    </row>
-    <row r="23" ht="57">
-      <c r="B23" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="26">
-        <v>5</v>
-      </c>
-      <c r="G23" s="40"/>
+      <c r="E23" s="23">
+        <v>5</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="24" ht="57">
       <c r="B24" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="15">
+        <v>5</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" ht="57">
+      <c r="B25" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="35">
+        <v>5</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" ht="57">
+      <c r="B26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="19">
+        <v>5</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" ht="57">
+      <c r="B27" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="37">
+        <v>3</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" ht="57">
+      <c r="B28" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="38">
+        <v>8</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" ht="42.75">
+      <c r="B29" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="D29" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="E29" s="39">
+        <v>3</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" ht="42.75">
+      <c r="B30" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="D30" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="F24" s="16">
-        <v>8</v>
-      </c>
-      <c r="G24" s="17"/>
-    </row>
-    <row r="25" ht="57">
-      <c r="B25" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" s="41">
-        <v>8</v>
-      </c>
-      <c r="G25" s="22"/>
-    </row>
-    <row r="26" ht="57">
-      <c r="B26" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="21">
-        <v>5</v>
-      </c>
-      <c r="G26" s="22"/>
-    </row>
-    <row r="27" ht="57">
-      <c r="B27" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" s="43">
+      <c r="E30" s="40">
         <v>3</v>
       </c>
-      <c r="G27" s="22"/>
-    </row>
-    <row r="28" ht="57">
-      <c r="B28" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="44">
-        <v>8</v>
-      </c>
-      <c r="G28" s="27"/>
-    </row>
-    <row r="29" ht="42.75">
-      <c r="B29" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="45">
-        <v>3</v>
-      </c>
-      <c r="G29" s="32"/>
-    </row>
-    <row r="30" ht="42.75">
-      <c r="B30" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" s="46">
-        <v>3</v>
-      </c>
-      <c r="G30" s="40"/>
+      <c r="F30" s="34" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" ht="57">
       <c r="B31" s="13" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" s="16">
+        <v>56</v>
+      </c>
+      <c r="E31" s="15">
+        <v>5</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" ht="57">
+      <c r="B32" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="35">
+        <v>5</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" ht="42.75">
+      <c r="B33" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="40">
+        <v>3</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" ht="57">
+      <c r="B34" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="43">
+        <v>2</v>
+      </c>
+      <c r="F34" s="44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="D35" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G31" s="17"/>
-    </row>
-    <row r="32" ht="57">
-      <c r="B32" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" s="41">
-        <v>8</v>
-      </c>
-      <c r="G32" s="22"/>
-    </row>
-    <row r="33" ht="42.75">
-      <c r="B33" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="F33" s="46">
-        <v>3</v>
-      </c>
-      <c r="G33" s="27"/>
-    </row>
-    <row r="34" ht="57">
-      <c r="B34" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34" s="50">
-        <v>5</v>
-      </c>
-      <c r="G34" s="51"/>
-    </row>
-    <row r="35" ht="14.25">
-      <c r="E35" s="52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="53">
-        <f>SUM(F13:F34)</f>
-        <v>120</v>
+      <c r="E35" s="46">
+        <f>SUM(E13:E34)</f>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="O5mJHy0ukKPOr8Di3KTpE44BwJOcp+orMlh9xO42OUOfF1wcVZ6DnHIurUGeuQ3cg6s+xSnWbMilRkzzE52hTw==" saltValue="ZHjE9ECT6JLGntzd65jL9g==" spinCount="100000" autoFilter="1" deleteColumns="1" deleteRows="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertHyperlinks="1" insertRows="1" objects="0" pivotTables="1" scenarios="0" selectLockedCells="0" selectUnlockedCells="0" sheet="1" sort="1"/>
   <dataValidations count="1" disablePrompts="0">
     <dataValidation sqref="B4:B8" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
@@ -1847,7 +1759,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{09BB8211-5B0D-45A9-8802-F9F642820BFB}">
+          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{A491789D-33FE-4324-BC33-CF6B8CB06D32}">
             <xm:f>3</xm:f>
             <x14:dxf>
               <font>
@@ -1855,10 +1767,10 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F13:F34</xm:sqref>
+          <xm:sqref>E13:E34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="lessThanOrEqual" id="{A9EC28CA-90E4-44F3-8FE0-32656C7F0A1A}">
+          <x14:cfRule type="cellIs" priority="7" operator="lessThanOrEqual" id="{621659AE-3BB9-4F31-B6FD-E7E5C443857F}">
             <xm:f>3</xm:f>
             <x14:dxf>
               <font>
@@ -1872,10 +1784,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F13:F34</xm:sqref>
+          <xm:sqref>E13:E34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="notBetween" id="{3B2FCBEF-CCE7-4E53-8C5D-2B0883AC9268}">
+          <x14:cfRule type="cellIs" priority="6" operator="notBetween" id="{1CB83144-0E53-49D1-ACD6-5E9B38DCFEAA}">
             <xm:f>3</xm:f>
             <xm:f>8</xm:f>
             <x14:dxf>
@@ -1890,10 +1802,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F13:F34</xm:sqref>
+          <xm:sqref>E13:E34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="between" id="{DEF280EA-0099-4633-BBF2-379C4AB18D4D}">
+          <x14:cfRule type="cellIs" priority="5" operator="between" id="{D9ECC498-759E-4113-AF0C-6FF6F5A0B5FA}">
             <xm:f>4</xm:f>
             <xm:f>7</xm:f>
             <x14:dxf>
@@ -1908,10 +1820,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F13:F34</xm:sqref>
+          <xm:sqref>E13:E34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" id="{F4608307-6605-4A03-8D0F-504D7B2BDC85}">
+          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{C9C416E8-F46A-469F-B328-5E5348235630}">
             <xm:f>8</xm:f>
             <x14:dxf>
               <font>
@@ -1925,10 +1837,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F13:F34</xm:sqref>
+          <xm:sqref>E13:E34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="aboveAverage" priority="2" stdDev="0" id="{56553315-77DA-4C89-9131-296A3670719A}">
+          <x14:cfRule type="aboveAverage" priority="3" stdDev="0" id="{DBCBFC1D-BC2D-4E42-92C6-5A4FA61E3E8D}">
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -1944,7 +1856,7 @@
           <xm:sqref>C4:C8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="aboveAverage" priority="1" aboveAverage="0" stdDev="0" id="{E7FA339C-0920-4A26-A157-52581599B7CF}">
+          <x14:cfRule type="aboveAverage" priority="2" aboveAverage="0" stdDev="0" id="{755BB3AC-D42C-4BD3-88DC-81419C3E7F68}">
             <x14:dxf>
               <font>
                 <color rgb="FF006100"/>
@@ -1959,15 +1871,32 @@
           </x14:cfRule>
           <xm:sqref>C4:C8</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{543E6632-DA0C-419B-B3DA-03DDB1AE2DED}">
+            <xm:f>5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E34</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{C71EC464-344C-4E81-9097-7A8AE933C8F4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{22371375-5570-4B72-8497-72B6EB5465DB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$B$4:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>G13:G34</xm:sqref>
+          <xm:sqref>F13:F34</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Documentacion/1. Story Points y Asignacion de Responsabilidades.xlsx
+++ b/Documentacion/1. Story Points y Asignacion de Responsabilidades.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t xml:space="preserve">Integrantes Proyecto</t>
   </si>
@@ -97,15 +97,27 @@
     <t xml:space="preserve">Cantidad Historias de Usuario Asignadas</t>
   </si>
   <si>
+    <t xml:space="preserve">Estados Historia de Usuario</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sebastián Jiménez Arrieta</t>
   </si>
   <si>
+    <t xml:space="preserve">En Proceso</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brandon Guido Navarro</t>
   </si>
   <si>
+    <t>Completado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sebastián Obando Ramírez</t>
   </si>
   <si>
+    <t xml:space="preserve">No Entregado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Julián Solano Obando</t>
   </si>
   <si>
@@ -121,7 +133,7 @@
     <t>ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Historia de Usuario</t>
+    <t xml:space="preserve">Historia de Usuario (Primer Sprint)</t>
   </si>
   <si>
     <t xml:space="preserve">Story Points</t>
@@ -130,6 +142,9 @@
     <t xml:space="preserve">Asignado a</t>
   </si>
   <si>
+    <t>Estado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Usuarios y roles</t>
   </si>
   <si>
@@ -278,6 +293,219 @@
   </si>
   <si>
     <t xml:space="preserve">Servicio para Registrar y Consultar Bitácoras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historia de Usuario (Segundo Sprint)</t>
+  </si>
+  <si>
+    <t>Administración</t>
+  </si>
+  <si>
+    <t>ADM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plantilla General del Sitio Web </t>
+  </si>
+  <si>
+    <t>ADM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Inicio de Sesión y Autenticación</t>
+  </si>
+  <si>
+    <t>ADM3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla de Bienvenida, Windgets, Notificaciones, etc</t>
+  </si>
+  <si>
+    <t>ADM4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Usuarios</t>
+  </si>
+  <si>
+    <t>ADM5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Roles</t>
+  </si>
+  <si>
+    <t>ADM6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Parametrización</t>
+  </si>
+  <si>
+    <t>ADM7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Módulos</t>
+  </si>
+  <si>
+    <t>ADM8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Instituciones</t>
+  </si>
+  <si>
+    <t>ADM9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Carreras</t>
+  </si>
+  <si>
+    <t>ADM10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Cursos</t>
+  </si>
+  <si>
+    <t>ADM11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Profesores</t>
+  </si>
+  <si>
+    <t>ADM12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Periodos</t>
+  </si>
+  <si>
+    <t>ADM13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Grupos</t>
+  </si>
+  <si>
+    <t>ADM14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Prematriculas</t>
+  </si>
+  <si>
+    <t>ADM15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Flujo Matrícula</t>
+  </si>
+  <si>
+    <t>ADM16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Expedientes</t>
+  </si>
+  <si>
+    <t>ADM17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Cargar Desglose y Asignar/Modificar Notas</t>
+  </si>
+  <si>
+    <t>ADM18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Consultar Promedios por Estudiante</t>
+  </si>
+  <si>
+    <t>ADM19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Consultar Listados por Periodo</t>
+  </si>
+  <si>
+    <t>ADM20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Facturas Ligadas a Matriculas</t>
+  </si>
+  <si>
+    <t>ADM21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar Pagos</t>
+  </si>
+  <si>
+    <t>ADM22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Enviar Notificaciones por Correo</t>
+  </si>
+  <si>
+    <t>ADM23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Consultar Bitácoras</t>
+  </si>
+  <si>
+    <t>ADM24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla para Administrar "Mi Perfil" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historia de Usuario (Tercer Sprint)</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>MOB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plantilla General de la App Móvil</t>
+  </si>
+  <si>
+    <t>MOB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla Móvil de Inicio de Sesión y Autenticación</t>
+  </si>
+  <si>
+    <t>MOB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla Móvil con Resumenes de Estado, Widgets, etc</t>
+  </si>
+  <si>
+    <t>MOB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla Móvil para Consultar "Mi Expediente' y Actualizar Datos</t>
+  </si>
+  <si>
+    <t>MOB4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla Móvil para Realizar Prematrícula</t>
+  </si>
+  <si>
+    <t>MOB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla Móvil para Realizar Matrícula</t>
+  </si>
+  <si>
+    <t>MOB6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantalla Móvil para "Ver Mis Cursos" </t>
+  </si>
+  <si>
+    <t>Gateway</t>
+  </si>
+  <si>
+    <t>GTW1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gateway como punto único de entrada</t>
+  </si>
+  <si>
+    <t>GTW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autenticación y Autorización Centralizada</t>
   </si>
 </sst>
 </file>
@@ -390,7 +618,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="23">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -442,6 +670,21 @@
       <right style="thick">
         <color auto="1"/>
       </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color theme="1"/>
       </top>
@@ -489,6 +732,19 @@
       <bottom style="thick">
         <color auto="1"/>
       </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -551,9 +807,57 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
       <right style="none"/>
       <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
       <bottom style="thick">
         <color auto="1"/>
       </bottom>
@@ -564,6 +868,30 @@
         <color auto="1"/>
       </left>
       <right style="none"/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
       <top style="none"/>
       <bottom style="thick">
         <color auto="1"/>
@@ -577,15 +905,12 @@
     <xf fontId="2" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
     <xf fontId="3" fillId="4" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="73">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="4" fillId="6" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -597,20 +922,32 @@
     <xf fontId="0" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="6" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="3" borderId="4" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="4" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="4" borderId="5" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="2" borderId="6" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="6" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="4" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="8" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="8" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="5" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="9" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -619,100 +956,167 @@
     <xf fontId="4" fillId="9" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="8" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="9" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf fontId="6" fillId="0" borderId="10" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="9" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="12" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="9" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="14" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="10" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="12" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="9" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="12" numFmtId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="14" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="10" numFmtId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="14" numFmtId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="17" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="5" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="5" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="5" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="9" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="9" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="10" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="9" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="9" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="10" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="9" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="9" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="9" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="12" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="9" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="8" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="10" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="9" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="10" numFmtId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="12" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="8" numFmtId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="12" numFmtId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="14" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="0" borderId="4" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="6" numFmtId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="8" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="8" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="8" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -737,7 +1141,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="AskingMansOz" id="{A36F4E31-68DB-11C5-CF8D-E4A86219E6FC}" userId="AskingMansOz" providerId="Teamlab"/>
+  <person displayName="AskingMansOz" id="{A9933E08-2285-B9BF-868D-B69CDC4BF782}" userId="AskingMansOz" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -1221,7 +1625,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C4" dT="2026-09-19T09:13:08.03Z" personId="{A36F4E31-68DB-11C5-CF8D-E4A86219E6FC}" id="{04CB6911-E216-5FFA-A00E-331AF1FB8FD4}" done="0">
+  <threadedComment ref="C4" dT="2026-09-19T09:13:08.03Z" personId="{A9933E08-2285-B9BF-868D-B69CDC4BF782}" id="{04CB6911-E216-5FFA-A00E-331AF1FB8FD4}" done="1">
     <text xml:space="preserve">Mide la carga de trabajo del equipo con base en el promedio de puntos acumulados por los integrantes:
 * Verde: Por debajo del promedio (menor carga).
 * Amarillo: En el promedio exacto (carga equilibrada).
@@ -1229,7 +1633,7 @@
 Lo ideal es que la carga de trabajo se mantengan cerca del promedio.
 </text>
   </threadedComment>
-  <threadedComment ref="D4" dT="2026-09-25T19:25:05.93Z" personId="{A36F4E31-68DB-11C5-CF8D-E4A86219E6FC}" id="{6A98EA58-EBE2-D560-1FEC-96EE11A8B0CE}" done="0">
+  <threadedComment ref="D4" dT="2026-09-25T19:25:05.93Z" personId="{A9933E08-2285-B9BF-868D-B69CDC4BF782}" id="{6A98EA58-EBE2-D560-1FEC-96EE11A8B0CE}" done="1">
     <text xml:space="preserve">21.6 x Persona
 </text>
   </threadedComment>
@@ -1242,8 +1646,8 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="33.28125"/>
     <col customWidth="1" min="3" max="3" width="17.140625"/>
-    <col customWidth="1" min="4" max="4" width="47.7109375"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" style="1" width="11.34375"/>
+    <col customWidth="1" min="4" max="4" width="58.140625"/>
+    <col customWidth="1" min="5" max="5" style="1" width="12.421875"/>
     <col customWidth="1" min="6" max="6" width="27.00390625"/>
     <col customWidth="1" min="7" max="7" width="18.421875"/>
     <col bestFit="1" customWidth="1" min="8" max="8" width="11.421875"/>
@@ -1264,81 +1668,93 @@
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5">
-        <f t="shared" ref="C4:C8" si="0">SUMIF($F$13:$F$100,B4,$E$13:$E$100)</f>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4">
+        <f>SUMIF($F$13:$F$135,B4,$E$13:$E$135)</f>
         <v>21</v>
       </c>
-      <c r="D4" s="6">
-        <f t="shared" ref="D4:D8" si="1">COUNTIF($E$13:$F$100,B4)</f>
+      <c r="D4" s="5">
+        <f>COUNTIF($E$13:$F$135,B4)</f>
+        <v>5</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4">
+        <f>SUMIF($F$13:$F$135,B5,$E$13:$E$135)</f>
+        <v>21</v>
+      </c>
+      <c r="D5" s="5">
+        <f>COUNTIF($E$13:$F$135,B5)</f>
         <v>4</v>
       </c>
-      <c r="C5" s="5">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="F5" s="8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="42.75">
       <c r="B6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4">
+        <f>SUMIF($F$13:$F$135,B6,$E$13:$E$135)</f>
+        <v>20</v>
+      </c>
+      <c r="D6" s="5">
+        <f>COUNTIF($E$13:$F$135,B6)</f>
         <v>5</v>
       </c>
-      <c r="C6" s="5">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="D6" s="6">
-        <f t="shared" si="1"/>
-        <v>5</v>
+      <c r="F6" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" ht="28.5">
       <c r="B7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="5">
-        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C7" s="4">
+        <f>SUMIF($F$13:$F$135,B7,$E$13:$E$135)</f>
         <v>23</v>
       </c>
-      <c r="D7" s="6">
-        <f t="shared" si="1"/>
+      <c r="D7" s="5">
+        <f>COUNTIF($E$13:$F$135,B7)</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" ht="28.5">
-      <c r="B8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="5">
-        <f t="shared" si="0"/>
+      <c r="B8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4">
+        <f>SUMIF($F$13:$F$135,B8,$E$13:$E$135)</f>
         <v>23</v>
       </c>
-      <c r="D8" s="9">
-        <f t="shared" si="1"/>
+      <c r="D8" s="11">
+        <f>COUNTIF($E$13:$F$135,B8)</f>
         <v>4</v>
       </c>
-      <c r="H8" s="10"/>
+      <c r="H8" s="12"/>
     </row>
     <row r="9" ht="28.5">
-      <c r="B9" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="B9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="14">
         <f>SUM(C4:C8)</f>
         <v>108</v>
       </c>
@@ -1347,406 +1763,989 @@
     <row r="11" ht="15.6"/>
     <row r="12" ht="17.399999999999999" customHeight="1">
       <c r="B12" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="71.25">
+      <c r="B13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="18">
+        <v>8</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" ht="42.75">
+      <c r="B14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="23">
+        <v>5</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" ht="71.25">
+      <c r="B15" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="23">
+        <v>5</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" ht="28.5">
+      <c r="B16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="23">
+        <v>5</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" ht="71.25">
+      <c r="B17" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="28">
+        <v>8</v>
+      </c>
+      <c r="F17" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="G17" s="30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" ht="42.75">
+      <c r="B18" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="33">
+        <v>5</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" ht="57">
+      <c r="B19" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="23">
+        <v>5</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" ht="42.75">
+      <c r="B20" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="23">
+        <v>5</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" ht="57">
+      <c r="B21" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="23">
+        <v>5</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" ht="42.75">
+      <c r="B22" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="23">
+        <v>5</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" ht="57">
+      <c r="B23" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="28">
+        <v>5</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" ht="57">
+      <c r="B24" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="18">
+        <v>5</v>
+      </c>
+      <c r="F24" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="G24" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" ht="57">
+      <c r="B25" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="44">
+        <v>5</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" ht="57">
+      <c r="B26" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="23">
+        <v>5</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" ht="57">
+      <c r="B27" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="46">
+        <v>3</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="57">
+      <c r="B28" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="47">
+        <v>8</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" ht="42.75">
+      <c r="B29" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="49">
+        <v>3</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" ht="42.75">
+      <c r="B30" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="51">
+        <v>3</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" ht="57">
+      <c r="B31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="18">
+        <v>5</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" ht="57">
+      <c r="B32" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="44">
+        <v>5</v>
+      </c>
+      <c r="F32" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" ht="42.75">
+      <c r="B33" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="51">
+        <v>3</v>
+      </c>
+      <c r="F33" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" ht="57">
+      <c r="B34" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="54">
+        <v>2</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="56" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" ht="57">
+      <c r="B35" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" ht="57">
+      <c r="B36" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="33"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="50"/>
+    </row>
+    <row r="37" ht="57">
+      <c r="B37" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="23"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="39"/>
+    </row>
+    <row r="38" ht="57">
+      <c r="B38" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" s="23"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="39"/>
+    </row>
+    <row r="39" ht="57">
+      <c r="B39" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" s="23"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="39"/>
+    </row>
+    <row r="40" ht="57">
+      <c r="B40" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="23"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="39"/>
+    </row>
+    <row r="41" ht="57">
+      <c r="B41" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" s="23"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="39"/>
+    </row>
+    <row r="42" ht="57">
+      <c r="B42" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="E42" s="23"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="39"/>
+    </row>
+    <row r="43" ht="57">
+      <c r="B43" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" s="23"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="39"/>
+    </row>
+    <row r="44" ht="57">
+      <c r="B44" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="E44" s="23"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="39"/>
+    </row>
+    <row r="45" ht="57">
+      <c r="B45" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="23"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="39"/>
+    </row>
+    <row r="46" ht="57">
+      <c r="B46" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="E46" s="23"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="39"/>
+    </row>
+    <row r="47" ht="57">
+      <c r="B47" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" s="23"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="39"/>
+    </row>
+    <row r="48" ht="57">
+      <c r="B48" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48" s="23"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="39"/>
+    </row>
+    <row r="49" ht="57">
+      <c r="B49" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="E49" s="23"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="39"/>
+    </row>
+    <row r="50" ht="57">
+      <c r="B50" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="E50" s="23"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="39"/>
+    </row>
+    <row r="51" ht="57">
+      <c r="B51" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D51" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="E51" s="23"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="39"/>
+    </row>
+    <row r="52" ht="57">
+      <c r="B52" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D52" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="E52" s="23"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="39"/>
+    </row>
+    <row r="53" ht="57">
+      <c r="B53" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="E53" s="23"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="39"/>
+    </row>
+    <row r="54" ht="57">
+      <c r="B54" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="E54" s="23"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="39"/>
+    </row>
+    <row r="55" ht="57">
+      <c r="B55" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="E55" s="23"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="39"/>
+    </row>
+    <row r="56" ht="57">
+      <c r="B56" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56" s="23"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="39"/>
+    </row>
+    <row r="57" ht="57">
+      <c r="B57" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D57" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57" s="23"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="39"/>
+    </row>
+    <row r="58" ht="57">
+      <c r="B58" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="E58" s="23"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="39"/>
+    </row>
+    <row r="59" ht="57">
+      <c r="B59" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D59" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="E59" s="28"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="43"/>
+    </row>
+    <row r="60" ht="57">
+      <c r="B60" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" ht="57">
+      <c r="B61" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="D61" s="63" t="s">
+        <v>122</v>
+      </c>
+      <c r="E61" s="33"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="50"/>
+    </row>
+    <row r="62" s="64" customFormat="1" ht="57">
+      <c r="B62" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="D62" s="65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E62" s="23"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="39"/>
+    </row>
+    <row r="63" s="64" customFormat="1" ht="57">
+      <c r="B63" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="D63" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="E63" s="23"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="39"/>
+    </row>
+    <row r="64" s="64" customFormat="1" ht="57">
+      <c r="B64" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D64" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="E64" s="23"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="39"/>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="B65" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="D65" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="E65" s="23"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="39"/>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="B66" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="D66" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="E66" s="23"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="39"/>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="B67" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="C67" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="D67" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="E67" s="28"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="39"/>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="B68" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D68" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="E68" s="69"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="B69" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E69" s="70"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="D70" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" ht="71.25">
-      <c r="B13" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="15">
-        <v>8</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" ht="42.75">
-      <c r="B14" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="19">
-        <v>5</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" ht="71.25">
-      <c r="B15" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="19">
-        <v>5</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" ht="28.5">
-      <c r="B16" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="19">
-        <v>5</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" ht="71.25">
-      <c r="B17" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="23">
-        <v>8</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" ht="42.75">
-      <c r="B18" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="27">
-        <v>5</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" ht="57">
-      <c r="B19" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="19">
-        <v>5</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" ht="42.75">
-      <c r="B20" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="19">
-        <v>5</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" ht="57">
-      <c r="B21" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="19">
-        <v>5</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" ht="42.75">
-      <c r="B22" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="19">
-        <v>5</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" ht="57">
-      <c r="B23" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="23">
-        <v>5</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" ht="57">
-      <c r="B24" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="15">
-        <v>5</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" ht="57">
-      <c r="B25" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="35">
-        <v>5</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" ht="57">
-      <c r="B26" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="19">
-        <v>5</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" ht="57">
-      <c r="B27" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="37">
-        <v>3</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" ht="57">
-      <c r="B28" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" s="38">
-        <v>8</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" ht="42.75">
-      <c r="B29" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29" s="39">
-        <v>3</v>
-      </c>
-      <c r="F29" s="28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" ht="42.75">
-      <c r="B30" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="40">
-        <v>3</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" ht="57">
-      <c r="B31" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="15">
-        <v>5</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" ht="57">
-      <c r="B32" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32" s="35">
-        <v>5</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" ht="42.75">
-      <c r="B33" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="40">
-        <v>3</v>
-      </c>
-      <c r="F33" s="24" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" ht="57">
-      <c r="B34" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="E34" s="43">
-        <v>2</v>
-      </c>
-      <c r="F34" s="44" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25">
-      <c r="D35" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="46">
-        <f>SUM(E13:E34)</f>
+      <c r="E70" s="72">
+        <f>SUM(E13:E35,E36:E59,E61:E69)</f>
         <v>108</v>
       </c>
     </row>
+    <row r="71" ht="14.25">
+      <c r="E71" s="1"/>
+    </row>
+    <row r="72" ht="14.25">
+      <c r="E72" s="1"/>
+    </row>
+    <row r="73" ht="14.25">
+      <c r="E73" s="1"/>
+    </row>
+    <row r="74" ht="14.25">
+      <c r="E74" s="1"/>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="O5mJHy0ukKPOr8Di3KTpE44BwJOcp+orMlh9xO42OUOfF1wcVZ6DnHIurUGeuQ3cg6s+xSnWbMilRkzzE52hTw==" saltValue="ZHjE9ECT6JLGntzd65jL9g==" spinCount="100000" autoFilter="1" deleteColumns="1" deleteRows="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertHyperlinks="1" insertRows="1" objects="0" pivotTables="1" scenarios="0" selectLockedCells="0" selectUnlockedCells="0" sheet="1" sort="1"/>
+  <sheetProtection autoFilter="1" deleteColumns="1" deleteRows="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertHyperlinks="1" insertRows="1" pivotTables="1" selectLockedCells="0" selectUnlockedCells="0" sheet="0" sort="1"/>
   <dataValidations count="1" disablePrompts="0">
     <dataValidation sqref="B4:B8" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
@@ -1759,7 +2758,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{A491789D-33FE-4324-BC33-CF6B8CB06D32}">
+          <x14:cfRule type="cellIs" priority="24" operator="equal" id="{370C7978-F9B6-4714-9D99-48C09D8CA2E2}">
             <xm:f>3</xm:f>
             <x14:dxf>
               <font>
@@ -1767,10 +2766,10 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E13:E34</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="lessThanOrEqual" id="{621659AE-3BB9-4F31-B6FD-E7E5C443857F}">
+          <xm:sqref>E13:E34 E36:E59 E61:E69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="23" operator="lessThanOrEqual" id="{36324845-3C89-4439-9C3E-4AD1A02A73C7}">
             <xm:f>3</xm:f>
             <x14:dxf>
               <font>
@@ -1784,10 +2783,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E13:E34</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="notBetween" id="{1CB83144-0E53-49D1-ACD6-5E9B38DCFEAA}">
+          <xm:sqref>E13:E34 E36:E59 E61:E69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="22" operator="notBetween" id="{2BC38861-C069-4A25-9002-4477D3DB5BB4}">
             <xm:f>3</xm:f>
             <xm:f>8</xm:f>
             <x14:dxf>
@@ -1802,10 +2801,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E13:E34</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="between" id="{D9ECC498-759E-4113-AF0C-6FF6F5A0B5FA}">
+          <xm:sqref>E13:E34 E36:E59 E61:E69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="21" operator="between" id="{6440F931-C165-48AB-8AA4-B9CD520A433E}">
             <xm:f>4</xm:f>
             <xm:f>7</xm:f>
             <x14:dxf>
@@ -1820,10 +2819,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E13:E34</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{C9C416E8-F46A-469F-B328-5E5348235630}">
+          <xm:sqref>E13:E34 E36:E59 E61:E69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="20" operator="greaterThanOrEqual" id="{4970097A-6ADC-4676-BA5C-CEAD1C11D703}">
             <xm:f>8</xm:f>
             <x14:dxf>
               <font>
@@ -1837,10 +2836,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E13:E34</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="aboveAverage" priority="3" stdDev="0" id="{DBCBFC1D-BC2D-4E42-92C6-5A4FA61E3E8D}">
+          <xm:sqref>E13:E34 E36:E59 E61:E69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="aboveAverage" priority="19" stdDev="0" id="{F56CEAE9-54E1-4AC5-917B-DB879FE83529}">
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -1856,7 +2855,7 @@
           <xm:sqref>C4:C8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="aboveAverage" priority="2" aboveAverage="0" stdDev="0" id="{755BB3AC-D42C-4BD3-88DC-81419C3E7F68}">
+          <x14:cfRule type="aboveAverage" priority="18" aboveAverage="0" stdDev="0" id="{D92F8707-FF4A-4A45-A510-CCC5AF0AD93B}">
             <x14:dxf>
               <font>
                 <color rgb="FF006100"/>
@@ -1872,7 +2871,7 @@
           <xm:sqref>C4:C8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{543E6632-DA0C-419B-B3DA-03DDB1AE2DED}">
+          <x14:cfRule type="cellIs" priority="17" operator="lessThan" id="{848D5610-41A5-4E9C-A973-474CBA58AEFD}">
             <xm:f>5</xm:f>
             <x14:dxf>
               <font>
@@ -1886,17 +2885,1402 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E34</xm:sqref>
+          <xm:sqref>E34 E36:E59 E61:E69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="16" text="Completado" id="{2AE373B2-70CB-4185-941C-C3174C7BEB3E}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G13</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="15" text="En Proceso" id="{BF564519-45E1-4CFA-A527-2D96E62688B6}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G13</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="14" text="No Entregado" id="{E0501E34-00AF-4A33-8A2C-5DEDA3F8C0F1}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G13</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="25" text="Completado" id="{1EF929BE-3F89-4E62-AA27-CA66743438E4}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G14</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="26" text="En Proceso" id="{39364251-73D1-499A-89CA-87AF608FAB95}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G14</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="27" text="No Entregado" id="{5710A9B5-9192-4780-B650-390094731A75}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G14</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="28" text="Completado" id="{CCFF4C89-FD13-4BFA-9CF2-EAA734859DAA}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="29" text="En Proceso" id="{07C412AC-4749-461C-93AA-AF7D270F7F2A}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="30" text="No Entregado" id="{5505E7E6-C8AC-43BE-9E85-1333D0D6144D}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="31" text="Completado" id="{C93CA3B5-BF24-4C74-9131-A3AEFC81D279}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="32" text="En Proceso" id="{2BCC7CF9-1508-49DC-AA67-A4A2A1C70A1F}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="33" text="No Entregado" id="{83FAB4F1-7F3F-4A5F-816A-426434320A37}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="34" text="Completado" id="{706C2A4A-6CAC-440B-BAB7-9A196880CAF6}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="35" text="En Proceso" id="{C0CDD7B4-D6D8-4347-ABAD-E5962C5D60EF}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="36" text="No Entregado" id="{D0DABEA1-108C-4132-82A4-9416AE376DF2}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="13" text="En Proceso" id="{53B66A31-1514-40A1-87A3-DBCBB6C2C3D9}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G18:G23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="12" text="Completado" id="{027EEBF6-F74C-42B9-B7EB-BE5547728F3B}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G18:G23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="11" text="No Entregado" id="{EB8C58FA-CD83-4CE2-81E2-721E924992EA}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G18:G23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="37" text="Completado" id="{8DAAC16F-E043-4A6E-BDC8-25C5A05C0A1F}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="38" text="En Proceso" id="{1E1D9829-37A8-45B1-853D-B9C3B8AECA88}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="39" text="No Entregado" id="{64C062E1-773D-49A6-B363-5A2F4995767E}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="40" text="Completado" id="{4C80A5E4-7776-4C40-A8DB-16DC2F388E72}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="41" text="En Proceso" id="{CC020AEA-B3C4-415F-9636-B9795A57B93F}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="42" text="No Entregado" id="{DAA317D2-312B-4FD8-86A7-B9EBD898ACDB}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="43" text="Completado" id="{93268C52-A42B-40D0-A0F1-02536F971241}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="44" text="En Proceso" id="{C78A8C18-895F-4760-A9BC-9CF151F0EA2E}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="45" text="No Entregado" id="{0CA721C5-965B-4348-BFEB-F31023E41D49}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="46" text="Completado" id="{0691BDED-5BCC-4C59-9039-374A30DDA062}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G27</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="47" text="En Proceso" id="{8BAB915B-5E07-4082-BD19-8B6CDA36A236}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G27</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="48" text="No Entregado" id="{85CE0FBD-1628-4107-9210-9B8C55330E90}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G27</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="49" text="Completado" id="{146F487F-E27C-4107-92AA-2E4D80035CEF}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G28</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="50" text="En Proceso" id="{1DB1C44D-A02D-49C5-830C-5677CFCE31D3}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G28</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="51" text="No Entregado" id="{DE150632-D222-4168-B324-E14D89F0132D}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G28</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="52" text="En Proceso" id="{E05A674E-A0F4-42DC-9E4F-40123F1CED68}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G29:G30</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="53" text="Completado" id="{A8DFAD1B-5965-4140-83C0-041F6C23A272}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G29:G30</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="54" text="No Entregado" id="{CD09D3DE-F879-452B-932B-EA480E168590}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G29:G30</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="55" text="Completado" id="{2817C1E5-4AAF-427F-AEF2-4739404F57C8}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="56" text="En Proceso" id="{12A9B999-C351-4DC1-A7B4-FBDDBEE88389}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="57" text="No Entregado" id="{D6E79353-9FB0-4CE0-B59C-14323C96ED30}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="58" text="Completado" id="{BDB3820B-14C5-4A3F-A593-40BD0721DF25}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="59" text="En Proceso" id="{022CCC51-E342-47F1-9A0E-B1A5B23251F8}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="60" text="No Entregado" id="{435A108D-5AC5-4C25-B759-BDE10AACE5AD}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="61" text="Completado" id="{9A4F4120-69AC-4663-8A91-5315B713C915}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="62" text="En Proceso" id="{1E0DE176-0EF6-44E8-BF3F-DD3C8EA1638F}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="63" text="No Entregado" id="{8865F5F9-676B-45CF-B1AF-D6F3F4E76D88}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="64" text="En Proceso" id="{7C17A3FC-1EBD-4530-A9D3-9FED3C8ECB12}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="65" text="Completado" id="{3A42E4FB-2F86-4C99-B531-DCE485ADDDF5}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="66" text="No Entregado" id="{0AEA1D89-16AA-4815-AF72-B19272C36B45}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="67" text="Completado" id="{66B9574D-3D1A-46FC-BC17-97F0511C27D9}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G36</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="68" text="En Proceso" id="{34B60BEB-67BD-4942-A9C4-2E4C28F1773C}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G36</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="69" text="No Entregado" id="{941AA1E6-F58C-4BEC-8F26-A48F32F1B82A}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G36</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="70" text="Completado" id="{5931A810-2ECA-4318-921B-43FC1BDAD064}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G37</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="71" text="En Proceso" id="{C6B03B5F-2900-4F68-82B7-A5392B53239D}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G37</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="72" text="No Entregado" id="{71EB7C5C-2F3E-463A-92FA-CCA1A9B1E5D2}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G37</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="73" text="Completado" id="{921CA6D0-73C5-4BE2-B198-EC5EB103A659}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G38</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="74" text="En Proceso" id="{0EDB6437-3207-4FC8-8D6E-6F2F3C53ED2C}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G38</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="75" text="No Entregado" id="{7383CB69-69BF-48C1-B509-0AC6C23D01C9}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G38</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="76" text="Completado" id="{CEBB8584-6B9E-455F-A601-736FBFC7219D}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G39:G59</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="77" text="En Proceso" id="{E8E4D52B-0C2A-4D73-A843-05A52858AFB0}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G39:G59</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="78" text="No Entregado" id="{7125D3A1-888F-4808-B417-103AF1CF4165}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G39:G59</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="79" text="En Proceso" id="{0A88F667-CD54-4FEA-BD1F-2F5B19CE153B}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G61:G67</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="80" text="Completado" id="{2EE0C6F7-2222-4D6A-AD67-57B7538808A3}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G61:G67</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="81" text="No Entregado" id="{A9DF775E-3830-4215-9BE6-01A0B1D56E31}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G18)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G61:G67</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="82" text="Completado" id="{CFC203FD-C83D-4C29-9464-8A90AF5F27A6}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G68</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="83" text="En Proceso" id="{ED5437B7-96A8-44A6-88BE-47D37B01993D}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G68</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="84" text="No Entregado" id="{5700FB87-50C1-4ED1-8A93-A17636044E48}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G68</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="85" text="Completado" id="{F4D79D4C-87F7-4B44-ACF0-C78010C1DA49}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="86" text="En Proceso" id="{E0F25A73-410B-426C-9156-7EC8FCAE6C77}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="87" text="No Entregado" id="{9D0DE07C-F3DD-448A-AEDB-2D3A614B025B}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="10" text="Completado" id="{0BD0CFF7-7D27-47CC-9FCA-629C492D0D2E}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G13:G34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="9" text="En Desarrollo" id="{767E9077-619E-4B7A-B616-DBAF9101BA71}">
+            <xm:f>NOT(ISERROR(SEARCH("En Desarrollo",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G13:G34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="8" text="En Proceso" id="{14343EF8-69E2-4990-A3CE-0E42E5367BDF}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G13:G34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="7" text="No Entregado" id="{CE4D4C0C-F34B-4C95-A839-531520BD3D83}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G13)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G13:G34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="6" text="Completado" id="{E2C22D59-24B2-421E-878D-11D23B283FEB}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G36)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G36:G59</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="5" text="En Proceso" id="{C019EC03-4D78-4642-9A93-9D4DA32038A4}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G36)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G36:G59</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="4" text="No Entregado" id="{0B7770B1-EB4E-43EA-8B73-0D2BE65A8818}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G36)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G36:G59</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="3" text="Completado" id="{C65255BC-5E2E-446D-AA35-2AAB13343B0C}">
+            <xm:f>NOT(ISERROR(SEARCH("Completado",G61)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G61:G69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="2" text="En Proceso" id="{EB24F533-6E9A-4C58-9A5C-95FBA4320DC5}">
+            <xm:f>NOT(ISERROR(SEARCH("En Proceso",G61)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G61:G69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" text="No Entregado" id="{7F6BB284-8CEB-4B7C-8CD5-4F696E4E7923}">
+            <xm:f>NOT(ISERROR(SEARCH("No Entregado",G61)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G61:G69</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{22371375-5570-4B72-8497-72B6EB5465DB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8" disablePrompts="0">
+        <x14:dataValidation xr:uid="{53EC063D-FB16-4465-A0B8-730CB216547B}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$B$4:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>F13:F34</xm:sqref>
+          <xm:sqref>F13:F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{AC7F6920-50CA-474B-884D-E669AE24AB21}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>$F$4:$F$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>G13:G17</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{16425DD8-631A-4547-8E67-6B73BDF1037F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>$F$4:$F$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>G18:G23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{12E32699-2BB9-4D97-9637-CFF5B3CD6960}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>$F$4:$F$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>G24:G28</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{BA9C1174-118F-4F26-94A9-C2E8670A881A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>$F$4:$F$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>G29:G30</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{1F3C5BEB-E26C-4CD3-995B-3720E64AF146}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>$F$4:$F$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>G31:G33</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{C56120BF-6220-438C-8A48-A08240A42579}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>$F$4:$F$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>G34</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{458F28CC-EF98-4364-9391-95A6E8364E24}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>$F$4:$F$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>G36:G59 G61:G69</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
